--- a/output/pdf_financials_xlsx/VIO.xlsx
+++ b/output/pdf_financials_xlsx/VIO.xlsx
@@ -19605,7 +19605,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">

--- a/output/pdf_financials_xlsx/VIO.xlsx
+++ b/output/pdf_financials_xlsx/VIO.xlsx
@@ -2123,55 +2123,55 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.001643</v>
+        <v>0.002106</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.000789</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.000705</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.00091</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.001434</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.001676</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.001871</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.002208</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.004111</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.004867</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.002025</v>
       </c>
       <c r="N28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
     </row>
     <row r="29">
@@ -2181,55 +2181,55 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.285097</v>
+        <v>-1.284634</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.465514</v>
+        <v>-0.464725</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.137379</v>
+        <v>1.138084</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.751049</v>
+        <v>1.751959</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.27884</v>
+        <v>-3.277406</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.760433</v>
+        <v>-0.758757</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.755175</v>
+        <v>-0.753152</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.044894</v>
+        <v>-0.043023</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>4.490839</v>
+        <v>4.493047</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.679176</v>
+        <v>-0.675065</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.728679</v>
+        <v>-0.723812</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.298755</v>
+        <v>0.30078</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>0.464989</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-2.901222</v>
+        <v>-2.853234</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-1.414812</v>
+        <v>-1.366824</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-1.166684</v>
+        <v>-1.118696</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.8131429999999999</v>
+        <v>-0.765155</v>
       </c>
     </row>
     <row r="30">
@@ -2239,40 +2239,40 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-910.7251943560561</v>
+        <v>-910.3970745604399</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-503.4434278545627</v>
+        <v>-502.5901412411048</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>583.4957034756958</v>
+        <v>583.8573810439913</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1050.091753022452</v>
+        <v>1050.63747361351</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-3042.865760289546</v>
+        <v>-3041.534963574776</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-628.4258631803382</v>
+        <v>-627.0408078938234</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-2707.78801678081</v>
+        <v>-2700.534260819678</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-59.03376814643383</v>
+        <v>-56.57347990742689</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>81.15323403888519</v>
+        <v>81.1931344540989</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-106.245590542682</v>
+        <v>-105.6024941689571</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-482.520941628315</v>
+        <v>-479.2980829718903</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>110.1681164978372</v>
+        <v>110.9148502291827</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>2071.220489977728</v>
@@ -6357,55 +6357,55 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>0.002106</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.000789</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.000705</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.00091</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.001434</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.001676</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.002023</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.001871</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.002208</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.004111</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.004867</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.002025</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
       <c r="R100" s="3" t="n">
-        <v>0</v>
+        <v>0.047988</v>
       </c>
     </row>
     <row r="101">
@@ -25597,7 +25597,11 @@
           <t>Depreciation of property and equipment 44,363</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -28830,7 +28834,11 @@
           <t>Depreciation of right-of-use assets</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -32036,7 +32044,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -39306,7 +39318,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E315" s="5" t="n">
         <v>0.000463</v>
       </c>
@@ -42621,7 +42637,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E348" s="5" t="n">
@@ -44455,7 +44471,11 @@
           <t>Depreciation of property and equipment 9 44,363</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -46336,7 +46356,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -48521,7 +48545,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -50107,7 +50135,11 @@
           <t>Depreciation of property plant and equipment</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -52502,7 +52534,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E449" s="5" t="n">
         <v>0.000463</v>
       </c>
@@ -57636,7 +57672,7 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E501" s="5" t="n">

--- a/output/pdf_financials_xlsx/VIO.xlsx
+++ b/output/pdf_financials_xlsx/VIO.xlsx
@@ -755,46 +755,46 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.02698</v>
+        <v>0.117416</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.025961</v>
+        <v>0.101773</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.030994</v>
+        <v>0.111826</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.031248</v>
+        <v>0.105271</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.032748</v>
+        <v>0.096222</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.030553</v>
+        <v>0.08225200000000001</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.001115</v>
+        <v>0.053584</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.0008720000000000001</v>
+        <v>0.068285</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.00127</v>
+        <v>0.087954</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.034271</v>
+        <v>0.117511</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.021085</v>
+        <v>0.09062099999999999</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.027998</v>
+        <v>0.113036</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>0.431302</v>
+        <v>0.473393</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.511501</v>
+        <v>0.560878</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>0.419623</v>
@@ -3794,7 +3794,7 @@
         <v>0</v>
       </c>
       <c r="R56" s="3" t="n">
-        <v>0</v>
+        <v>1.79752</v>
       </c>
     </row>
     <row r="57">
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="R57" s="3" t="n">
-        <v>0</v>
+        <v>0.27029</v>
       </c>
     </row>
     <row r="58">
@@ -26787,7 +26787,11 @@
           <t>Private placement -</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26888,7 +26892,11 @@
           <t>Flow-through private placement -</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -28561,7 +28569,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -29893,7 +29905,11 @@
           <t>Private placement</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -29988,7 +30004,11 @@
           <t>Flow-through private placement</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -39821,7 +39841,11 @@
           <t>Future income taxes</t>
         </is>
       </c>
-      <c r="D320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E320" s="5" t="n">
         <v>-0.565399</v>
       </c>
@@ -47702,7 +47726,11 @@
           <t>Rent and office expenses</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E399" s="5" t="n">
         <v>0.090436</v>
       </c>
